--- a/document/Scene.xlsx
+++ b/document/Scene.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sekiguchi\Documents\HouseholdAccountBook\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34156685-0CC2-4CBE-BEBD-8CFE2C3855FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86845479-EB1E-4A33-8A3B-C22C67944AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="画面一覧" sheetId="1" r:id="rId1"/>
     <sheet name="ユーザー登録画面" sheetId="2" r:id="rId2"/>
+    <sheet name="ログイン画面" sheetId="3" r:id="rId3"/>
+    <sheet name="収支情報追加画面" sheetId="4" r:id="rId4"/>
+    <sheet name="収支一覧画面" sheetId="5" r:id="rId5"/>
+    <sheet name="収支レポート画面" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -278,6 +282,281 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>541262</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>226785</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>564349</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>199640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26173212-77D7-A757-CDC2-516330B8310A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="541262" y="226785"/>
+          <a:ext cx="5272420" cy="7190688"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>231321</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>23086</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>44103</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E71084C7-037D-9203-B989-DE7E890EEE20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="656167" y="1162654"/>
+          <a:ext cx="5272419" cy="7263449"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3023</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>208644</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>75441</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>116416</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F789C910-8822-6F7B-88DD-22E730CCBD62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="659190" y="208644"/>
+          <a:ext cx="5321751" cy="7358439"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>14816</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>86283</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>89773</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E06F462E-5EF3-DF24-1E24-42DB3ACF66BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="670983" y="209550"/>
+          <a:ext cx="5320800" cy="7330890"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>37600</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>217018</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE68C5F0-4D3B-486F-73D5-1033AF34913F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="228600"/>
+          <a:ext cx="5320800" cy="7303618"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -634,5 +913,50 @@
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{860809DE-8DB7-440A-AAE8-72DFB9A6F30A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B86F867-C9AB-45A9-A23B-3D6339BDB6F1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95D89AB8-1711-46DE-AF02-C408FF890FC6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DEC392-3ACB-45DA-A960-2B3411FDB37F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/document/Scene.xlsx
+++ b/document/Scene.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sekiguchi\Documents\HouseholdAccountBook\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86845479-EB1E-4A33-8A3B-C22C67944AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FA073F-FFA9-49ED-A775-A06851C770C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="画面一覧" sheetId="1" r:id="rId1"/>
-    <sheet name="ユーザー登録画面" sheetId="2" r:id="rId2"/>
-    <sheet name="ログイン画面" sheetId="3" r:id="rId3"/>
-    <sheet name="収支情報追加画面" sheetId="4" r:id="rId4"/>
-    <sheet name="収支一覧画面" sheetId="5" r:id="rId5"/>
-    <sheet name="収支レポート画面" sheetId="6" r:id="rId6"/>
+    <sheet name="画面遷移図" sheetId="7" r:id="rId2"/>
+    <sheet name="ユーザー登録画面" sheetId="2" r:id="rId3"/>
+    <sheet name="ログイン画面" sheetId="3" r:id="rId4"/>
+    <sheet name="収支情報追加画面" sheetId="4" r:id="rId5"/>
+    <sheet name="収支一覧画面" sheetId="5" r:id="rId6"/>
+    <sheet name="収支レポート画面" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="203">
   <si>
     <t>画面一覧</t>
     <rPh sb="0" eb="4">
@@ -205,6 +206,1932 @@
     </rPh>
     <rPh sb="17" eb="19">
       <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要素一覧</t>
+    <rPh sb="0" eb="4">
+      <t>ヨウソイチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項番</t>
+    <rPh sb="0" eb="2">
+      <t>コウバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>種類</t>
+    <rPh sb="0" eb="2">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字列</t>
+    <rPh sb="0" eb="3">
+      <t>モジレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目名</t>
+    <rPh sb="0" eb="3">
+      <t>コウモクメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブタイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー名タイトル</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>概要</t>
+    <rPh sb="0" eb="2">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>家計簿アプリ</t>
+    <rPh sb="0" eb="3">
+      <t>カケイボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規登録してください</t>
+    <rPh sb="0" eb="4">
+      <t>シンキトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー名入力</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード入力</t>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリアイコン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規登録ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキストボックス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字列を表示</t>
+    <rPh sb="0" eb="3">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最小入力桁数</t>
+    <rPh sb="0" eb="2">
+      <t>サイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>ニュウリョクケタスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大入力桁数</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規登録</t>
+    <rPh sb="0" eb="4">
+      <t>シンキトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーアイコン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像でアプリアイコンを表示</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BootstrapIconsで人型アイコンを表示</t>
+    <rPh sb="15" eb="17">
+      <t>ヒトガタ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーからの入力を受け、文字の入力行う</t>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワードアイコン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BootstrapIconsで鍵アイコンを表示</t>
+    <rPh sb="15" eb="16">
+      <t>カギ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目名</t>
+    <rPh sb="0" eb="2">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内容</t>
+    <rPh sb="0" eb="2">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー名入力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・空文字チェック-&gt;エラーテキスト「ユーザー名を入力してください」表示
+・入力桁数チェック-&gt;エラーテキスト「4～10桁で入力してください」表示</t>
+    <rPh sb="1" eb="4">
+      <t>カラモジ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ケタスウ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・空文字チェック-&gt;エラーテキスト「パスワードを入力してください」表示
+・入力桁数チェック-&gt;エラーテキスト「4～12桁で入力してください」表示</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規登録ボタン</t>
+    <rPh sb="0" eb="4">
+      <t>シンキトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログインしてください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログインリンクテキスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規登録リンクテキスト</t>
+    <rPh sb="0" eb="4">
+      <t>シンキトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログインボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チェックリスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・DBに同じユーザー名、パスワードで登録済みかチェック-&gt;エラーテキスト「すでに登録済みのユーザーです」表示</t>
+    <rPh sb="4" eb="5">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・DBに同じユーザー名、パスワードで登録済みかチェック-&gt;エラーテキスト「未登録のユーザーです」表示</t>
+    <rPh sb="4" eb="5">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーからの入力を受け、文字の入力行う
+デフォルトで入力内容は隠している状態</t>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>ニュウリョクナイヨウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リンク付き文字列を表示
+押下時にユーザー登録画面へ遷移</t>
+    <rPh sb="3" eb="4">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>オウカジ</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>押下時に入力された内容でログインを行う</t>
+    <rPh sb="0" eb="3">
+      <t>オウカジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リンク付き文字列を表示
+押下時にログイン画面へ遷移</t>
+    <rPh sb="3" eb="4">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一覧</t>
+    <rPh sb="0" eb="2">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収支追加</t>
+    <rPh sb="0" eb="4">
+      <t>シュウシツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レポート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログアウト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘッダーアプリアイコン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘッダータイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘッダー一覧</t>
+    <rPh sb="4" eb="6">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘッダー収支追加</t>
+    <rPh sb="4" eb="8">
+      <t>シュウシツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘッダーレポート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加内容タイトル</t>
+    <rPh sb="0" eb="4">
+      <t>ツイカナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加内容タイトル入力</t>
+    <rPh sb="8" eb="10">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>種別タイトル</t>
+    <rPh sb="0" eb="2">
+      <t>シュベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出トグル</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チェックボックス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入トグル</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額タイトル</t>
+    <rPh sb="0" eb="2">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額入力</t>
+    <rPh sb="0" eb="2">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付タイトル</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付入力</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付選択ボックス</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額</t>
+    <rPh sb="0" eb="2">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加する</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>押下時に入力された内容でDBにユーザー追加を行う</t>
+    <rPh sb="0" eb="3">
+      <t>オウカジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>押下時に入力された内容でDBに収支情報追加を行う</t>
+    <rPh sb="0" eb="3">
+      <t>オウカジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カレンダーアイコンから日付を選択
+選択した日付の文字列を表示</t>
+    <rPh sb="11" eb="13">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーからの入力を受け、文字の入力を行う
+デフォルトで入力内容は隠している状態</t>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーからの入力を受け、文字の入力を行う</t>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーからの入力を受け、数字の入力を行う</t>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リンク付き文字列を表示
+押下時に収支一覧画面へ遷移</t>
+    <rPh sb="3" eb="4">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リンク付き文字列を表示
+押下時に収支情報追加画面へ遷移</t>
+    <rPh sb="3" eb="4">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リンク付き文字列を表示
+押下時に収支レポート画面へ遷移</t>
+    <rPh sb="3" eb="4">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>押下時に選択状態となる。
+支出トグルと収入トグルはどちらかのみ選択状態とする。</t>
+    <rPh sb="0" eb="3">
+      <t>オウカジ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>センタクジョウタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>押下時に選択状態となる。
+支出トグルと収入トグルはどちらかのみ選択状態とする。</t>
+    <rPh sb="0" eb="2">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加内容タイトル入力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・空文字チェック-&gt;エラーテキスト「タイトルを入力してください」表示
+・入力桁数チェック-&gt;エラーテキスト「タイトルは1～20桁で入力してください」表示</t>
+    <rPh sb="1" eb="4">
+      <t>カラモジ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ケタスウ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・空文字チェック-&gt;エラーテキスト「金額を入力してください」表示
+・入力桁数チェック-&gt;エラーテキスト「金額は1～10桁で入力してください」表示</t>
+    <rPh sb="18" eb="20">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・空文字チェック-&gt;エラーテキスト「パスワードを入力してください」表示
+・入力桁数チェック-&gt;エラーテキスト「パスワードは4～12桁で入力してください」表示</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・空文字チェック-&gt;エラーテキスト「ユーザー名を入力してください」表示
+・入力桁数チェック-&gt;エラーテキスト「ユーザー名は4～10桁で入力してください」表示</t>
+    <rPh sb="1" eb="4">
+      <t>カラモジ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ケタスウ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘッダーログアウト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リンク付き文字列を表示
+ログアウトし、ログイン画面へ遷移</t>
+    <rPh sb="23" eb="25">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検索開始日付入力</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検索終了日付入力</t>
+    <rPh sb="2" eb="4">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検索ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検索</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>押下時に入力された検索開始日付～検索終了日付にあてはまる収支情報をDBから取得し、リストに表示を行う</t>
+    <rPh sb="0" eb="3">
+      <t>オウカジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="16" eb="22">
+      <t>ケンサクシュウリョウヒヅケ</t>
+    </rPh>
+    <rPh sb="28" eb="32">
+      <t>シュウシジョウホウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストヘッダータイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストヘッダー日付</t>
+    <rPh sb="7" eb="9">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストヘッダー種別</t>
+    <rPh sb="7" eb="9">
+      <t>シュベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストヘッダー金額</t>
+    <rPh sb="7" eb="9">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストアイテム日付</t>
+    <rPh sb="7" eb="9">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>種別</t>
+    <rPh sb="0" eb="2">
+      <t>シュベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストアイテムタイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストアイテム種別</t>
+    <rPh sb="7" eb="9">
+      <t>シュベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストアイテム金額</t>
+    <rPh sb="7" eb="9">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収支一覧</t>
+    <rPh sb="0" eb="4">
+      <t>シュウシイチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期間タイトル</t>
+    <rPh sb="0" eb="2">
+      <t>キカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期間</t>
+    <rPh sb="0" eb="2">
+      <t>キカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収支レポート</t>
+    <rPh sb="0" eb="2">
+      <t>シュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示期間タイトル</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示期間</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示期間プルダウン</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プルダウン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プルダウンから選択が可能
+選択肢は直近6ヶ月のみとする。</t>
+    <rPh sb="7" eb="9">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>チョッキン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>図形</t>
+    <rPh sb="0" eb="2">
+      <t>ズケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入凡例図</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンレイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青色の四角形を表示</t>
+    <rPh sb="0" eb="2">
+      <t>アオイロ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>シカクケイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入タイトル</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出凡例図</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンレイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出タイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額（円）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入グラフ（5か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額（最大）</t>
+    <rPh sb="0" eb="2">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額（中間1）</t>
+    <rPh sb="3" eb="5">
+      <t>チュウカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額（中間2）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額（0）</t>
+    <rPh sb="0" eb="2">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入、支出合計金額で高いほうの金額から、最大桁数を1繰り上げ、ほかの桁を0にした数値を表示
+例：252455の場合　300000</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ゴウケイキンガク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>サイダイケタスウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額（最大）から2/3の数値を表示</t>
+    <rPh sb="12" eb="14">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額（最大）から1/3の数値を表示</t>
+    <rPh sb="12" eb="14">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5か月前の収入合計金額をグラフとして表示</t>
+    <rPh sb="5" eb="11">
+      <t>シュウニュウゴウケイキンガク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出グラフ（5か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5か月前の支出合計金額をグラフとして表示</t>
+    <rPh sb="5" eb="7">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入グラフ（4か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出グラフ（4か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入グラフ（3か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出グラフ（3か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入グラフ（2か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出グラフ（2か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入グラフ（1か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出グラフ（1か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収入グラフ（今月）</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コンゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出グラフ（今月）</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今月の支出合計金額をグラフとして表示</t>
+    <rPh sb="3" eb="5">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今月の収入合計金額をグラフとして表示</t>
+    <rPh sb="3" eb="9">
+      <t>シュウニュウゴウケイキンガク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1か月前の支出合計金額をグラフとして表示</t>
+    <rPh sb="5" eb="7">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1か月前の収入合計金額をグラフとして表示</t>
+    <rPh sb="5" eb="11">
+      <t>シュウニュウゴウケイキンガク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2か月前の支出合計金額をグラフとして表示</t>
+    <rPh sb="5" eb="7">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2か月前の収入合計金額をグラフとして表示</t>
+    <rPh sb="5" eb="11">
+      <t>シュウニュウゴウケイキンガク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3か月前の支出合計金額をグラフとして表示</t>
+    <rPh sb="5" eb="7">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3か月前の収入合計金額をグラフとして表示</t>
+    <rPh sb="5" eb="11">
+      <t>シュウニュウゴウケイキンガク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4か月前の支出合計金額をグラフとして表示</t>
+    <rPh sb="5" eb="7">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4か月前の収入合計金額をグラフとして表示</t>
+    <rPh sb="5" eb="11">
+      <t>シュウニュウゴウケイキンガク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今月タイトル</t>
+    <rPh sb="0" eb="2">
+      <t>コンゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今月</t>
+    <rPh sb="0" eb="2">
+      <t>コンゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今月のグラフの上に文字列を表示</t>
+    <rPh sb="0" eb="2">
+      <t>コンゲツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付（5か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゲツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付（4か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゲツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付（3か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゲツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付（2か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゲツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付（1か月前）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゲツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付（今月）</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コンゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5か月前の日付（年月）文字列を表示</t>
+    <rPh sb="5" eb="7">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4か月前の日付（年月）文字列を表示</t>
+    <rPh sb="5" eb="7">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3か月前の日付（年月）文字列を表示</t>
+    <rPh sb="5" eb="7">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2か月前の日付（年月）文字列を表示</t>
+    <rPh sb="5" eb="7">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1か月前の日付（年月）文字列を表示</t>
+    <rPh sb="5" eb="7">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今月の日付（年月）文字列を表示</t>
+    <rPh sb="0" eb="2">
+      <t>コンゲツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集計タイトル</t>
+    <rPh sb="0" eb="2">
+      <t>シュウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「今月の日付（年月）＋"の集計"」文字列を表示</t>
+  </si>
+  <si>
+    <t>集計収入タイトル</t>
+    <rPh sb="0" eb="4">
+      <t>シュウケイシュウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集計収入</t>
+  </si>
+  <si>
+    <t>収支</t>
+    <rPh sb="0" eb="2">
+      <t>シュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集計支出タイトル</t>
+    <rPh sb="0" eb="2">
+      <t>シュウケイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集計支出</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集計収支タイトル</t>
+    <rPh sb="0" eb="2">
+      <t>シュウケイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集計収支</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択した月の収入合計金額の文字列を表示</t>
+    <rPh sb="13" eb="16">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択した月の支出合計金額の文字列を表示</t>
+    <rPh sb="6" eb="8">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択した月の収入合計金額と支出合計金額の差額の文字列を表示</t>
+    <rPh sb="13" eb="15">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サガク</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>補足</t>
+    <rPh sb="0" eb="2">
+      <t>ホソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※グラフは月ごとの合計金額を表示しています</t>
+    <rPh sb="5" eb="6">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>ゴウケイキンガク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -237,7 +2164,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -260,13 +2187,82 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -286,6 +2282,1011 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73F520F1-0A62-1C77-6C4E-5ACAA09AA576}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="228600"/>
+          <a:ext cx="1530350" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ユーザー登録画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C5D2F45-BCB3-465C-8238-BE0FB07002D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="1600200"/>
+          <a:ext cx="1530350" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ログイン画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直線矢印コネクタ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1575420A-BB65-C2EF-1060-8D4C81952660}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="3" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1425575" y="723900"/>
+          <a:ext cx="0" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A43F857-261C-4399-9304-571FA93670C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3962400" y="228600"/>
+          <a:ext cx="1530350" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>収支情報追加画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD92B86C-66DE-4DFA-84A9-4199102DF525}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3962400" y="1600200"/>
+          <a:ext cx="1530350" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>収支一覧画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9FB17EC-301A-4020-9CF8-8A0D9AAC59FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3962400" y="2755900"/>
+          <a:ext cx="1530350" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>収支レポート画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線矢印コネクタ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBA22553-872C-4BF8-8785-4A45B329C958}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="9" idx="2"/>
+          <a:endCxn id="10" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4727575" y="723900"/>
+          <a:ext cx="0" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="直線矢印コネクタ 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDFA09E6-8D51-4AF9-AD31-84DD53DF19F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="10" idx="2"/>
+          <a:endCxn id="11" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4727575" y="2095500"/>
+          <a:ext cx="0" cy="660400"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線矢印コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{461F57B4-E3E5-CA22-9ED6-6413B222295D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="3" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2190750" y="1847850"/>
+          <a:ext cx="1111250" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="コネクタ: カギ線 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0EFB7CA-D6CD-F5CA-A30A-55C6D11C26FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="9" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="2228850" y="476250"/>
+          <a:ext cx="1733550" cy="1181100"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 82601"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104776</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="コネクタ: カギ線 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F43E03C9-C348-46BD-9415-73F6D7E8769F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="11" idx="1"/>
+          <a:endCxn id="3" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="1425576" y="2095500"/>
+          <a:ext cx="2536825" cy="908050"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="32" name="コネクタ: カギ線 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2EA3140-1173-556F-8A0E-9DAEF8B7DC47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="9" idx="3"/>
+          <a:endCxn id="11" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5492750" y="476250"/>
+          <a:ext cx="12700" cy="2527300"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 1800000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="直線矢印コネクタ 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FDC7C7C-0696-3886-8342-E99BAF7FB3C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="10" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3302000" y="1847850"/>
+          <a:ext cx="660400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="889987" cy="328423"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="69" name="テキスト ボックス 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0FC6665-113F-6755-EEE2-3A210D02DF60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2717800" y="190500"/>
+          <a:ext cx="889987" cy="328423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ログアウト</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>654050</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="889987" cy="328423"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="70" name="テキスト ボックス 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09309195-B860-4EED-93E4-CE92882F6FA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2635250" y="2673350"/>
+          <a:ext cx="889987" cy="328423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ログアウト</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="889987" cy="328423"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="72" name="テキスト ボックス 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94ED1EBA-211A-4564-BC14-A038A6463A8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2279650" y="1892300"/>
+          <a:ext cx="889987" cy="328423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ログアウト</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="748923" cy="328423"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="73" name="テキスト ボックス 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D46B75D-4687-4BD4-9854-B5A4FDA3F7DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3016250" y="1511300"/>
+          <a:ext cx="748923" cy="328423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ログイン</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -296,7 +3297,7 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>564349</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>199640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -339,7 +3340,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -351,7 +3352,7 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>23086</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>44103</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -394,20 +3395,20 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>3023</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>208644</xdr:rowOff>
+      <xdr:rowOff>208645</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>75441</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>116416</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>105833</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -436,63 +3437,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="659190" y="208644"/>
-          <a:ext cx="5321751" cy="7358439"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>14816</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>86283</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>89773</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E06F462E-5EF3-DF24-1E24-42DB3ACF66BA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="670983" y="209550"/>
-          <a:ext cx="5320800" cy="7330890"/>
+          <a:off x="659190" y="208645"/>
+          <a:ext cx="5321751" cy="6839855"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -515,16 +3461,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>37600</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>217018</xdr:rowOff>
+      <xdr:colOff>71467</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>154121</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="10" name="図 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE68C5F0-4D3B-486F-73D5-1033AF34913F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF971CA9-7432-E710-D75A-90C31851B3B3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -546,8 +3492,63 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="660400" y="228600"/>
-          <a:ext cx="5320800" cy="7303618"/>
+          <a:off x="656167" y="232833"/>
+          <a:ext cx="5320800" cy="7731788"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>71467</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>100041</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A5E193C-4D93-C0EE-52B2-4B86D7536233}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="656167" y="232833"/>
+          <a:ext cx="5320800" cy="6989791"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -907,7 +3908,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E00C226-5344-4E0F-99CE-34E063C592E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC5D964-9FDD-4F81-B128-8A0DDCDB8764}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData/>
@@ -918,10 +3919,405 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{860809DE-8DB7-440A-AAE8-72DFB9A6F30A}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E00C226-5344-4E0F-99CE-34E063C592E3}">
+  <dimension ref="K3:Q24"/>
   <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
+  <cols>
+    <col min="11" max="11" width="8.6640625" style="2"/>
+    <col min="12" max="12" width="23.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.25" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="46.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="11:17">
+      <c r="K3" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="11:17">
+      <c r="K4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="11:17">
+      <c r="K5" s="3">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="11:17">
+      <c r="K6" s="3">
+        <v>2</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="11:17">
+      <c r="K7" s="3">
+        <v>3</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="11:17">
+      <c r="K8" s="3">
+        <v>4</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="11:17">
+      <c r="K9" s="3">
+        <v>5</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="1">
+        <v>4</v>
+      </c>
+      <c r="P9" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="11:17">
+      <c r="K10" s="3">
+        <v>6</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O10" s="1">
+        <v>4</v>
+      </c>
+      <c r="P10" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="11:17">
+      <c r="K11" s="3">
+        <v>7</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="11:17">
+      <c r="K12" s="3">
+        <v>8</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O12" s="1">
+        <v>8</v>
+      </c>
+      <c r="P12" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="11:17" ht="36">
+      <c r="K13" s="3">
+        <v>9</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="1">
+        <v>8</v>
+      </c>
+      <c r="P13" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="11:17">
+      <c r="K14" s="3">
+        <v>10</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="11:17" ht="36">
+      <c r="K15" s="3">
+        <v>11</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="11:17">
+      <c r="K16" s="3">
+        <v>12</v>
+      </c>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+    </row>
+    <row r="17" spans="11:17">
+      <c r="K17" s="3">
+        <v>13</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+    </row>
+    <row r="18" spans="11:17">
+      <c r="K18" s="3">
+        <v>14</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+    </row>
+    <row r="20" spans="11:17">
+      <c r="K20" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="11:17">
+      <c r="K21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="7"/>
+    </row>
+    <row r="22" spans="11:17" ht="35.5" customHeight="1">
+      <c r="K22" s="3">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+    </row>
+    <row r="23" spans="11:17" ht="39" customHeight="1">
+      <c r="K23" s="3">
+        <v>2</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="7"/>
+    </row>
+    <row r="24" spans="11:17">
+      <c r="K24" s="3">
+        <v>3</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="M24:Q24"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -929,10 +4325,407 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B86F867-C9AB-45A9-A23B-3D6339BDB6F1}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{860809DE-8DB7-440A-AAE8-72DFB9A6F30A}">
+  <dimension ref="K7:Q28"/>
   <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
+  <cols>
+    <col min="12" max="12" width="19.6640625" customWidth="1"/>
+    <col min="13" max="13" width="13.9140625" customWidth="1"/>
+    <col min="14" max="14" width="24.6640625" customWidth="1"/>
+    <col min="15" max="15" width="15.5" customWidth="1"/>
+    <col min="16" max="16" width="17.83203125" customWidth="1"/>
+    <col min="17" max="17" width="42.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="11:17">
+      <c r="K7" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="11:17">
+      <c r="K8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="11:17">
+      <c r="K9" s="3">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="11:17">
+      <c r="K10" s="3">
+        <v>2</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="11:17">
+      <c r="K11" s="3">
+        <v>3</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="11:17">
+      <c r="K12" s="3">
+        <v>4</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="11:17">
+      <c r="K13" s="3">
+        <v>5</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="1">
+        <v>4</v>
+      </c>
+      <c r="P13" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="11:17">
+      <c r="K14" s="3">
+        <v>6</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O14" s="1">
+        <v>4</v>
+      </c>
+      <c r="P14" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="11:17">
+      <c r="K15" s="3">
+        <v>7</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="11:17">
+      <c r="K16" s="3">
+        <v>8</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O16" s="1">
+        <v>8</v>
+      </c>
+      <c r="P16" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="11:17" ht="36">
+      <c r="K17" s="3">
+        <v>9</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O17" s="1">
+        <v>8</v>
+      </c>
+      <c r="P17" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q17" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="11:17">
+      <c r="K18" s="3">
+        <v>10</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="11:17" ht="36">
+      <c r="K19" s="3">
+        <v>11</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="11:17">
+      <c r="K20" s="3">
+        <v>12</v>
+      </c>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+    <row r="21" spans="11:17">
+      <c r="K21" s="3">
+        <v>13</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+    </row>
+    <row r="22" spans="11:17">
+      <c r="K22" s="3">
+        <v>14</v>
+      </c>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+    </row>
+    <row r="23" spans="11:17">
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="11:17">
+      <c r="K24" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="11:17">
+      <c r="K25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="7"/>
+    </row>
+    <row r="26" spans="11:17" ht="39.5" customHeight="1">
+      <c r="K26" s="3">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+    </row>
+    <row r="27" spans="11:17" ht="35.5" customHeight="1">
+      <c r="K27" s="3">
+        <v>2</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="7"/>
+    </row>
+    <row r="28" spans="11:17">
+      <c r="K28" s="3">
+        <v>3</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="M26:Q26"/>
+    <mergeCell ref="M27:Q27"/>
+    <mergeCell ref="M28:Q28"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -940,10 +4733,507 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95D89AB8-1711-46DE-AF02-C408FF890FC6}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B86F867-C9AB-45A9-A23B-3D6339BDB6F1}">
+  <dimension ref="K2:Q26"/>
   <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
+  <cols>
+    <col min="12" max="12" width="22.83203125" customWidth="1"/>
+    <col min="13" max="13" width="38.83203125" customWidth="1"/>
+    <col min="14" max="14" width="22.25" customWidth="1"/>
+    <col min="17" max="17" width="48.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="11:17">
+      <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="11:17">
+      <c r="K3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="11:17">
+      <c r="K4" s="3">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="11:17">
+      <c r="K5" s="3">
+        <v>2</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="11:17" ht="36">
+      <c r="K6" s="3">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="11:17" ht="36">
+      <c r="K7" s="3">
+        <v>4</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="11:17" ht="36">
+      <c r="K8" s="3">
+        <v>5</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="11:17" ht="36">
+      <c r="K9" s="3">
+        <v>6</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="11:17">
+      <c r="K10" s="3">
+        <v>7</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="11:17">
+      <c r="K11" s="3">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="11:17">
+      <c r="K12" s="3">
+        <v>9</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="11:17" ht="19.5" customHeight="1">
+      <c r="K13" s="3">
+        <v>10</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="11:17" ht="36">
+      <c r="K14" s="3">
+        <v>11</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="11:17" ht="37.5" customHeight="1">
+      <c r="K15" s="3">
+        <v>12</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="11:17">
+      <c r="K16" s="3">
+        <v>13</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="11:17">
+      <c r="K17" s="3">
+        <v>14</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1</v>
+      </c>
+      <c r="P17" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="11:17">
+      <c r="K18" s="3">
+        <v>15</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="11:17" ht="36">
+      <c r="K19" s="3">
+        <v>16</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="11:17">
+      <c r="K20" s="3">
+        <v>17</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="11:17">
+      <c r="K21" s="3">
+        <v>18</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+    </row>
+    <row r="22" spans="11:17">
+      <c r="K22" s="15"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+    </row>
+    <row r="23" spans="11:17" ht="18" customHeight="1">
+      <c r="K23" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="11:17" ht="18" customHeight="1">
+      <c r="K24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="7"/>
+    </row>
+    <row r="25" spans="11:17" ht="39.5" customHeight="1">
+      <c r="K25" s="3">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="13"/>
+    </row>
+    <row r="26" spans="11:17" ht="39.5" customHeight="1">
+      <c r="K26" s="3">
+        <v>2</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="M26:Q26"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -951,10 +5241,1712 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95D89AB8-1711-46DE-AF02-C408FF890FC6}">
+  <dimension ref="K2:Q25"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="12" max="12" width="26.58203125" customWidth="1"/>
+    <col min="13" max="13" width="20.08203125" customWidth="1"/>
+    <col min="14" max="14" width="15.08203125" customWidth="1"/>
+    <col min="15" max="15" width="13.9140625" customWidth="1"/>
+    <col min="16" max="16" width="13.83203125" customWidth="1"/>
+    <col min="17" max="17" width="53" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="11:17">
+      <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="11:17">
+      <c r="K3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="11:17">
+      <c r="K4" s="3">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="11:17">
+      <c r="K5" s="3">
+        <v>2</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="11:17" ht="36">
+      <c r="K6" s="3">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="11:17" ht="36">
+      <c r="K7" s="3">
+        <v>4</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="11:17" ht="36">
+      <c r="K8" s="3">
+        <v>5</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="11:17" ht="36">
+      <c r="K9" s="3">
+        <v>6</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="11:17">
+      <c r="K10" s="3">
+        <v>7</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="11:17">
+      <c r="K11" s="3">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="11:17" ht="36">
+      <c r="K12" s="3">
+        <v>9</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="11:17" ht="36">
+      <c r="K13" s="3">
+        <v>10</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="11:17" ht="36">
+      <c r="K14" s="3">
+        <v>11</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="11:17">
+      <c r="K15" s="3">
+        <v>12</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="11:17">
+      <c r="K16" s="3">
+        <v>13</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="11:17">
+      <c r="K17" s="3">
+        <v>14</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="11:17" ht="36">
+      <c r="K18" s="3">
+        <v>15</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="11:17" ht="36">
+      <c r="K19" s="3">
+        <v>16</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="11:17">
+      <c r="K20" s="3">
+        <v>17</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="11:17">
+      <c r="K21" s="3">
+        <v>18</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="11:17">
+      <c r="K22" s="3">
+        <v>19</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="11:17" ht="36">
+      <c r="K23" s="3">
+        <v>20</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q23" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="11:17">
+      <c r="K24" s="3">
+        <v>21</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+    </row>
+    <row r="25" spans="11:17">
+      <c r="K25" s="3">
+        <v>22</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="14"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DEC392-3ACB-45DA-A960-2B3411FDB37F}">
-  <dimension ref="A1"/>
+  <dimension ref="K2:Q56"/>
   <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
+  <cols>
+    <col min="12" max="12" width="20.33203125" customWidth="1"/>
+    <col min="13" max="13" width="21.4140625" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="17" max="17" width="65.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="11:17">
+      <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="11:17">
+      <c r="K3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="11:17">
+      <c r="K4" s="3">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="11:17">
+      <c r="K5" s="3">
+        <v>2</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="11:17" ht="36" customHeight="1">
+      <c r="K6" s="3">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="11:17" ht="36" customHeight="1">
+      <c r="K7" s="3">
+        <v>4</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="11:17" ht="36" customHeight="1">
+      <c r="K8" s="3">
+        <v>5</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="11:17" ht="36" customHeight="1">
+      <c r="K9" s="3">
+        <v>6</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="11:17" ht="36" customHeight="1">
+      <c r="K10" s="3">
+        <v>7</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="11:17" ht="36" customHeight="1">
+      <c r="K11" s="3">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="11:17" ht="36" customHeight="1">
+      <c r="K12" s="3">
+        <v>9</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="11:17" ht="36" customHeight="1">
+      <c r="K13" s="3">
+        <v>10</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="11:17">
+      <c r="K14" s="3">
+        <v>11</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="11:17">
+      <c r="K15" s="3">
+        <v>12</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="11:17">
+      <c r="K16" s="3">
+        <v>13</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="11:17">
+      <c r="K17" s="3">
+        <v>14</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="11:17" ht="54">
+      <c r="K18" s="3">
+        <v>15</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="11:17">
+      <c r="K19" s="3">
+        <v>16</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="11:17">
+      <c r="K20" s="3">
+        <v>17</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="11:17">
+      <c r="K21" s="3">
+        <v>18</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="11:17">
+      <c r="K22" s="3">
+        <v>19</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="11:17">
+      <c r="K23" s="3">
+        <v>20</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="11:17">
+      <c r="K24" s="3">
+        <v>21</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="11:17">
+      <c r="K25" s="3">
+        <v>22</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" spans="11:17">
+      <c r="K26" s="3">
+        <v>23</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" spans="11:17">
+      <c r="K27" s="3">
+        <v>24</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="11:17">
+      <c r="K28" s="3">
+        <v>25</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="11:17">
+      <c r="K29" s="3">
+        <v>26</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="11:17">
+      <c r="K30" s="3">
+        <v>27</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="11:17">
+      <c r="K31" s="3">
+        <v>28</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="11:17">
+      <c r="K32" s="3">
+        <v>29</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="11:17">
+      <c r="K33" s="3">
+        <v>30</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="11:17">
+      <c r="K34" s="3">
+        <v>31</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="35" spans="11:17">
+      <c r="K35" s="3">
+        <v>32</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="11:17">
+      <c r="K36" s="3">
+        <v>33</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="11:17">
+      <c r="K37" s="3">
+        <v>34</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="38" spans="11:17">
+      <c r="K38" s="3">
+        <v>35</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="11:17">
+      <c r="K39" s="3">
+        <v>36</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="40" spans="11:17">
+      <c r="K40" s="3">
+        <v>37</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="41" spans="11:17">
+      <c r="K41" s="3">
+        <v>38</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42" spans="11:17">
+      <c r="K42" s="3">
+        <v>39</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="11:17">
+      <c r="K43" s="3">
+        <v>40</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="44" spans="11:17">
+      <c r="K44" s="3">
+        <v>41</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="11:17">
+      <c r="K45" s="3">
+        <v>42</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46" spans="11:17">
+      <c r="K46" s="3">
+        <v>43</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="11:17">
+      <c r="K47" s="3">
+        <v>44</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="11:17" ht="54">
+      <c r="K48" s="3">
+        <v>45</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N48" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="11:17">
+      <c r="K49" s="3">
+        <v>46</v>
+      </c>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q49" s="1"/>
+    </row>
+    <row r="50" spans="11:17">
+      <c r="K50" s="3">
+        <v>47</v>
+      </c>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q50" s="1"/>
+    </row>
+    <row r="51" spans="11:17">
+      <c r="K51" s="3">
+        <v>48</v>
+      </c>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q51" s="1"/>
+    </row>
+    <row r="52" spans="11:17">
+      <c r="K52" s="3">
+        <v>49</v>
+      </c>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+    </row>
+    <row r="53" spans="11:17">
+      <c r="K53" s="3">
+        <v>50</v>
+      </c>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+    </row>
+    <row r="54" spans="11:17">
+      <c r="K54" s="3">
+        <v>51</v>
+      </c>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+    </row>
+    <row r="55" spans="11:17">
+      <c r="K55" s="3">
+        <v>52</v>
+      </c>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+    </row>
+    <row r="56" spans="11:17">
+      <c r="K56" s="3">
+        <v>53</v>
+      </c>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/document/Scene.xlsx
+++ b/document/Scene.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sekiguchi\Documents\HouseholdAccountBook\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FA073F-FFA9-49ED-A775-A06851C770C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F515BEA3-B84F-4149-A396-309BD0C84DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="画面一覧" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="203">
   <si>
     <t>画面一覧</t>
     <rPh sb="0" eb="4">
@@ -2228,7 +2228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2237,32 +2237,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -4065,11 +4058,11 @@
       <c r="N9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O9" s="1">
-        <v>4</v>
-      </c>
-      <c r="P9" s="1">
-        <v>10</v>
+      <c r="O9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Q9" s="1" t="s">
         <v>48</v>
@@ -4134,11 +4127,11 @@
       <c r="N12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O12" s="1">
-        <v>8</v>
-      </c>
-      <c r="P12" s="1">
-        <v>12</v>
+      <c r="O12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Q12" s="1" t="s">
         <v>51</v>
@@ -4163,7 +4156,7 @@
       <c r="P13" s="1">
         <v>12</v>
       </c>
-      <c r="Q13" s="11" t="s">
+      <c r="Q13" s="4" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4209,7 +4202,7 @@
       <c r="P15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q15" s="11" t="s">
+      <c r="Q15" s="4" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4258,13 +4251,13 @@
       <c r="L21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M21" s="5" t="s">
+      <c r="M21" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="7"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="9"/>
     </row>
     <row r="22" spans="11:17" ht="35.5" customHeight="1">
       <c r="K22" s="3">
@@ -4273,13 +4266,13 @@
       <c r="L22" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="M22" s="8" t="s">
+      <c r="M22" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
     </row>
     <row r="23" spans="11:17" ht="39" customHeight="1">
       <c r="K23" s="3">
@@ -4288,28 +4281,28 @@
       <c r="L23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M23" s="9" t="s">
+      <c r="M23" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="7"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="9"/>
     </row>
     <row r="24" spans="11:17">
       <c r="K24" s="3">
         <v>3</v>
       </c>
-      <c r="L24" s="10" t="s">
+      <c r="L24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="M24" s="5" t="s">
+      <c r="M24" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="7"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4568,7 +4561,7 @@
       <c r="P17" s="1">
         <v>12</v>
       </c>
-      <c r="Q17" s="11" t="s">
+      <c r="Q17" s="4" t="s">
         <v>98</v>
       </c>
     </row>
@@ -4614,7 +4607,7 @@
       <c r="P19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q19" s="11" t="s">
+      <c r="Q19" s="4" t="s">
         <v>66</v>
       </c>
     </row>
@@ -4666,13 +4659,13 @@
       <c r="L25" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M25" s="5" t="s">
+      <c r="M25" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="7"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="9"/>
     </row>
     <row r="26" spans="11:17" ht="39.5" customHeight="1">
       <c r="K26" s="3">
@@ -4681,13 +4674,13 @@
       <c r="L26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="M26" s="8" t="s">
+      <c r="M26" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
     </row>
     <row r="27" spans="11:17" ht="35.5" customHeight="1">
       <c r="K27" s="3">
@@ -4696,28 +4689,28 @@
       <c r="L27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M27" s="9" t="s">
+      <c r="M27" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="7"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="9"/>
     </row>
     <row r="28" spans="11:17">
       <c r="K28" s="3">
         <v>3</v>
       </c>
-      <c r="L28" s="10" t="s">
+      <c r="L28" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="M28" s="5" t="s">
+      <c r="M28" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="7"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4836,7 +4829,7 @@
       <c r="P6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="Q6" s="4" t="s">
         <v>101</v>
       </c>
     </row>
@@ -4859,7 +4852,7 @@
       <c r="P7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="4" t="s">
         <v>102</v>
       </c>
     </row>
@@ -4882,7 +4875,7 @@
       <c r="P8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="Q8" s="4" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4901,7 +4894,7 @@
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="11" t="s">
+      <c r="Q9" s="4" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5016,7 +5009,7 @@
       <c r="P14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="4" t="s">
         <v>104</v>
       </c>
     </row>
@@ -5039,7 +5032,7 @@
       <c r="P15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q15" s="11" t="s">
+      <c r="Q15" s="4" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5131,7 +5124,7 @@
       <c r="P19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q19" s="11" t="s">
+      <c r="Q19" s="4" t="s">
         <v>97</v>
       </c>
     </row>
@@ -5163,20 +5156,14 @@
         <v>18</v>
       </c>
       <c r="L21" s="1"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="11:17">
-      <c r="K22" s="15"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
+      <c r="K22" s="2"/>
     </row>
     <row r="23" spans="11:17" ht="18" customHeight="1">
       <c r="K23" s="2" t="s">
@@ -5190,13 +5177,13 @@
       <c r="L24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M24" s="5" t="s">
+      <c r="M24" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="7"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="9"/>
     </row>
     <row r="25" spans="11:17" ht="39.5" customHeight="1">
       <c r="K25" s="3">
@@ -5205,13 +5192,13 @@
       <c r="L25" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="M25" s="9" t="s">
+      <c r="M25" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="13"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="12"/>
     </row>
     <row r="26" spans="11:17" ht="39.5" customHeight="1">
       <c r="K26" s="3">
@@ -5220,13 +5207,13 @@
       <c r="L26" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="M26" s="9" t="s">
+      <c r="M26" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="13"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5346,7 +5333,7 @@
       <c r="P6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="Q6" s="4" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5369,7 +5356,7 @@
       <c r="P7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="4" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5392,7 +5379,7 @@
       <c r="P8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="Q8" s="4" t="s">
         <v>103</v>
       </c>
     </row>
@@ -5415,7 +5402,7 @@
       <c r="P9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q9" s="11" t="s">
+      <c r="Q9" s="4" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5484,7 +5471,7 @@
       <c r="P12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="Q12" s="4" t="s">
         <v>97</v>
       </c>
     </row>
@@ -5507,7 +5494,7 @@
       <c r="P13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q13" s="11" t="s">
+      <c r="Q13" s="4" t="s">
         <v>97</v>
       </c>
     </row>
@@ -5530,7 +5517,7 @@
       <c r="P14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="4" t="s">
         <v>117</v>
       </c>
     </row>
@@ -5622,7 +5609,7 @@
       <c r="P18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q18" s="11" t="s">
+      <c r="Q18" s="4" t="s">
         <v>104</v>
       </c>
     </row>
@@ -5645,7 +5632,7 @@
       <c r="P19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q19" s="11" t="s">
+      <c r="Q19" s="4" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5737,7 +5724,7 @@
       <c r="P23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q23" s="11" t="s">
+      <c r="Q23" s="4" t="s">
         <v>97</v>
       </c>
     </row>
@@ -5757,11 +5744,11 @@
         <v>22</v>
       </c>
       <c r="L25" s="1"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="14"/>
+      <c r="Q25" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -5876,7 +5863,7 @@
       <c r="P6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="Q6" s="4" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5899,7 +5886,7 @@
       <c r="P7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="4" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5922,7 +5909,7 @@
       <c r="P8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="Q8" s="4" t="s">
         <v>103</v>
       </c>
     </row>
@@ -5945,7 +5932,7 @@
       <c r="P9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q9" s="11" t="s">
+      <c r="Q9" s="4" t="s">
         <v>112</v>
       </c>
     </row>
@@ -6014,7 +6001,7 @@
       <c r="P12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="Q12" s="4" t="s">
         <v>135</v>
       </c>
     </row>
@@ -6037,7 +6024,7 @@
       <c r="P13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q13" s="11" t="s">
+      <c r="Q13" s="4" t="s">
         <v>138</v>
       </c>
     </row>
@@ -6083,7 +6070,7 @@
       <c r="P15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q15" s="11" t="s">
+      <c r="Q15" s="4" t="s">
         <v>138</v>
       </c>
     </row>
@@ -6152,7 +6139,7 @@
       <c r="P18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q18" s="11" t="s">
+      <c r="Q18" s="4" t="s">
         <v>148</v>
       </c>
     </row>
@@ -6833,7 +6820,7 @@
       <c r="M48" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N48" s="11" t="s">
+      <c r="N48" s="4" t="s">
         <v>202</v>
       </c>
       <c r="O48" s="1" t="s">

--- a/document/Scene.xlsx
+++ b/document/Scene.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sekiguchi\Documents\HouseholdAccountBook\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F515BEA3-B84F-4149-A396-309BD0C84DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2981CE-4FF8-48BD-BD19-B4BF70DEBA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="画面一覧" sheetId="1" r:id="rId1"/>
@@ -465,40 +465,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・空文字チェック-&gt;エラーテキスト「ユーザー名を入力してください」表示
-・入力桁数チェック-&gt;エラーテキスト「4～10桁で入力してください」表示</t>
-    <rPh sb="1" eb="4">
-      <t>カラモジ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ケタスウ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>ケタ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・空文字チェック-&gt;エラーテキスト「パスワードを入力してください」表示
-・入力桁数チェック-&gt;エラーテキスト「4～12桁で入力してください」表示</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>新規登録ボタン</t>
     <rPh sb="0" eb="4">
       <t>シンキトウロク</t>
@@ -1118,40 +1084,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・空文字チェック-&gt;エラーテキスト「パスワードを入力してください」表示
-・入力桁数チェック-&gt;エラーテキスト「パスワードは4～12桁で入力してください」表示</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・空文字チェック-&gt;エラーテキスト「ユーザー名を入力してください」表示
-・入力桁数チェック-&gt;エラーテキスト「ユーザー名は4～10桁で入力してください」表示</t>
-    <rPh sb="1" eb="4">
-      <t>カラモジ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ケタスウ</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>ケタ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ヘッダーログアウト</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2133,6 +2065,71 @@
     <rPh sb="14" eb="16">
       <t>ヒョウジ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・空文字チェック-&gt;エラーテキスト「ユーザー名を入力してください」表示
+・入力桁数チェック-&gt;エラーテキスト「ユーザー名は4～10文字で入力してください」表示</t>
+    <rPh sb="1" eb="4">
+      <t>カラモジ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ケタスウ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・空文字チェック-&gt;エラーテキスト「ユーザー名を入力してください」表示
+・入力桁数チェック-&gt;エラーテキスト「4～10文字で入力してください」表示</t>
+    <rPh sb="1" eb="4">
+      <t>カラモジ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ケタスウ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・空文字チェック-&gt;エラーテキスト「パスワードを入力してください」表示
+・入力桁数チェック-&gt;エラーテキスト「8～12文字で入力してください」表示</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・空文字チェック-&gt;エラーテキスト「パスワードを入力してください」表示
+・入力桁数チェック-&gt;エラーテキスト「パスワードは8～12文字で入力してください」表示</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4157,7 +4154,7 @@
         <v>12</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="11:17">
@@ -4180,7 +4177,7 @@
         <v>26</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="11:17" ht="36">
@@ -4188,7 +4185,7 @@
         <v>11</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>21</v>
@@ -4203,7 +4200,7 @@
         <v>26</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="11:17">
@@ -4241,7 +4238,7 @@
     </row>
     <row r="20" spans="11:17">
       <c r="K20" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="11:17">
@@ -4267,7 +4264,7 @@
         <v>54</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="N22" s="6"/>
       <c r="O22" s="6"/>
@@ -4282,7 +4279,7 @@
         <v>36</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>56</v>
+        <v>201</v>
       </c>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
@@ -4294,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
@@ -4415,7 +4412,7 @@
         <v>21</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>26</v>
@@ -4493,7 +4490,7 @@
         <v>10</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="11:17">
@@ -4562,7 +4559,7 @@
         <v>12</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="11:17">
@@ -4570,7 +4567,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>39</v>
@@ -4585,7 +4582,7 @@
         <v>26</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="11:17" ht="36">
@@ -4593,7 +4590,7 @@
         <v>11</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>21</v>
@@ -4608,7 +4605,7 @@
         <v>26</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="11:17">
@@ -4649,7 +4646,7 @@
     </row>
     <row r="24" spans="11:17">
       <c r="K24" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="11:17">
@@ -4675,7 +4672,7 @@
         <v>54</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>110</v>
+        <v>199</v>
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
@@ -4690,7 +4687,7 @@
         <v>36</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>109</v>
+        <v>202</v>
       </c>
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
@@ -4702,10 +4699,10 @@
         <v>3</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N28" s="8"/>
       <c r="O28" s="8"/>
@@ -4769,7 +4766,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>25</v>
@@ -4792,7 +4789,7 @@
         <v>2</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>21</v>
@@ -4815,13 +4812,13 @@
         <v>3</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>26</v>
@@ -4830,7 +4827,7 @@
         <v>26</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="11:17" ht="36">
@@ -4838,13 +4835,13 @@
         <v>4</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>26</v>
@@ -4853,7 +4850,7 @@
         <v>26</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="11:17" ht="36">
@@ -4861,13 +4858,13 @@
         <v>5</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>26</v>
@@ -4876,7 +4873,7 @@
         <v>26</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="11:17" ht="36">
@@ -4884,18 +4881,18 @@
         <v>6</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="11:17">
@@ -4909,7 +4906,7 @@
         <v>21</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>26</v>
@@ -4926,7 +4923,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>21</v>
@@ -4949,7 +4946,7 @@
         <v>9</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>40</v>
@@ -4964,7 +4961,7 @@
         <v>20</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="11:17" ht="19.5" customHeight="1">
@@ -4972,7 +4969,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>40</v>
@@ -4995,14 +4992,14 @@
         <v>11</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="O14" s="1" t="s">
         <v>26</v>
       </c>
@@ -5010,7 +5007,7 @@
         <v>26</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="11:17" ht="37.5" customHeight="1">
@@ -5018,14 +5015,14 @@
         <v>12</v>
       </c>
       <c r="L15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="O15" s="1" t="s">
         <v>26</v>
       </c>
@@ -5033,7 +5030,7 @@
         <v>26</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="11:17">
@@ -5041,13 +5038,13 @@
         <v>13</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>26</v>
@@ -5064,7 +5061,7 @@
         <v>14</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>40</v>
@@ -5079,7 +5076,7 @@
         <v>10</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="11:17">
@@ -5087,13 +5084,13 @@
         <v>15</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>26</v>
@@ -5110,10 +5107,10 @@
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>26</v>
@@ -5125,7 +5122,7 @@
         <v>26</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="11:17">
@@ -5133,22 +5130,22 @@
         <v>17</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>39</v>
       </c>
       <c r="N20" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="21" spans="11:17">
@@ -5167,7 +5164,7 @@
     </row>
     <row r="23" spans="11:17" ht="18" customHeight="1">
       <c r="K23" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="11:17" ht="18" customHeight="1">
@@ -5190,10 +5187,10 @@
         <v>1</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N25" s="11"/>
       <c r="O25" s="11"/>
@@ -5205,10 +5202,10 @@
         <v>2</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N26" s="11"/>
       <c r="O26" s="11"/>
@@ -5273,7 +5270,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>25</v>
@@ -5296,7 +5293,7 @@
         <v>2</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>21</v>
@@ -5319,13 +5316,13 @@
         <v>3</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>26</v>
@@ -5334,7 +5331,7 @@
         <v>26</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="11:17" ht="36">
@@ -5342,13 +5339,13 @@
         <v>4</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>26</v>
@@ -5357,7 +5354,7 @@
         <v>26</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="11:17" ht="36">
@@ -5365,13 +5362,13 @@
         <v>5</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>26</v>
@@ -5380,7 +5377,7 @@
         <v>26</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="11:17" ht="36">
@@ -5388,13 +5385,13 @@
         <v>6</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>26</v>
@@ -5403,7 +5400,7 @@
         <v>26</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="11:17">
@@ -5417,7 +5414,7 @@
         <v>21</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>26</v>
@@ -5434,13 +5431,13 @@
         <v>8</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>26</v>
@@ -5457,10 +5454,10 @@
         <v>9</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>26</v>
@@ -5472,7 +5469,7 @@
         <v>26</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="11:17" ht="36">
@@ -5480,10 +5477,10 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>26</v>
@@ -5495,7 +5492,7 @@
         <v>26</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="11:17" ht="36">
@@ -5503,13 +5500,13 @@
         <v>11</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>39</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>26</v>
@@ -5518,7 +5515,7 @@
         <v>26</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="11:17">
@@ -5526,13 +5523,13 @@
         <v>12</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>26</v>
@@ -5549,7 +5546,7 @@
         <v>13</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>21</v>
@@ -5564,7 +5561,7 @@
         <v>26</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="11:17">
@@ -5572,13 +5569,13 @@
         <v>14</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>26</v>
@@ -5595,13 +5592,13 @@
         <v>15</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>26</v>
@@ -5610,7 +5607,7 @@
         <v>26</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="11:17" ht="36">
@@ -5618,7 +5615,7 @@
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>21</v>
@@ -5633,7 +5630,7 @@
         <v>26</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="11:17">
@@ -5641,7 +5638,7 @@
         <v>17</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>21</v>
@@ -5664,7 +5661,7 @@
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>21</v>
@@ -5679,7 +5676,7 @@
         <v>26</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="11:17">
@@ -5687,7 +5684,7 @@
         <v>19</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>21</v>
@@ -5710,10 +5707,10 @@
         <v>20</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>26</v>
@@ -5725,7 +5722,7 @@
         <v>26</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="11:17">
@@ -5803,7 +5800,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>25</v>
@@ -5826,7 +5823,7 @@
         <v>2</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>21</v>
@@ -5849,13 +5846,13 @@
         <v>3</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>26</v>
@@ -5864,7 +5861,7 @@
         <v>26</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="11:17" ht="36" customHeight="1">
@@ -5872,13 +5869,13 @@
         <v>4</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>26</v>
@@ -5887,7 +5884,7 @@
         <v>26</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="11:17" ht="36" customHeight="1">
@@ -5895,13 +5892,13 @@
         <v>5</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>26</v>
@@ -5910,7 +5907,7 @@
         <v>26</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="11:17" ht="36" customHeight="1">
@@ -5918,13 +5915,13 @@
         <v>6</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>26</v>
@@ -5933,7 +5930,7 @@
         <v>26</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="11:17" ht="36" customHeight="1">
@@ -5947,7 +5944,7 @@
         <v>21</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>26</v>
@@ -5964,13 +5961,13 @@
         <v>8</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>26</v>
@@ -5987,10 +5984,10 @@
         <v>9</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>26</v>
@@ -6002,7 +5999,7 @@
         <v>26</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="11:17" ht="36" customHeight="1">
@@ -6010,10 +6007,10 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>26</v>
@@ -6025,7 +6022,7 @@
         <v>26</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="11:17">
@@ -6033,13 +6030,13 @@
         <v>11</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>26</v>
@@ -6056,10 +6053,10 @@
         <v>12</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>26</v>
@@ -6071,7 +6068,7 @@
         <v>26</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="11:17">
@@ -6079,13 +6076,13 @@
         <v>13</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>26</v>
@@ -6102,13 +6099,13 @@
         <v>14</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>26</v>
@@ -6125,7 +6122,7 @@
         <v>15</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>21</v>
@@ -6140,7 +6137,7 @@
         <v>26</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="11:17">
@@ -6148,7 +6145,7 @@
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>21</v>
@@ -6163,7 +6160,7 @@
         <v>26</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="11:17">
@@ -6171,7 +6168,7 @@
         <v>17</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>21</v>
@@ -6186,7 +6183,7 @@
         <v>26</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="11:17">
@@ -6194,7 +6191,7 @@
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>21</v>
@@ -6217,10 +6214,10 @@
         <v>19</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>26</v>
@@ -6232,7 +6229,7 @@
         <v>26</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="11:17">
@@ -6240,10 +6237,10 @@
         <v>20</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>26</v>
@@ -6255,7 +6252,7 @@
         <v>26</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="11:17">
@@ -6263,10 +6260,10 @@
         <v>21</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>26</v>
@@ -6278,7 +6275,7 @@
         <v>26</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="11:17">
@@ -6286,10 +6283,10 @@
         <v>22</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>26</v>
@@ -6301,7 +6298,7 @@
         <v>26</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="11:17">
@@ -6309,10 +6306,10 @@
         <v>23</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>26</v>
@@ -6324,7 +6321,7 @@
         <v>26</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="11:17">
@@ -6332,10 +6329,10 @@
         <v>24</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>26</v>
@@ -6347,7 +6344,7 @@
         <v>26</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="11:17">
@@ -6355,10 +6352,10 @@
         <v>25</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>26</v>
@@ -6370,7 +6367,7 @@
         <v>26</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="11:17">
@@ -6378,10 +6375,10 @@
         <v>26</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>26</v>
@@ -6393,7 +6390,7 @@
         <v>26</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="11:17">
@@ -6401,10 +6398,10 @@
         <v>27</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>26</v>
@@ -6416,7 +6413,7 @@
         <v>26</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="11:17">
@@ -6424,10 +6421,10 @@
         <v>28</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>26</v>
@@ -6439,7 +6436,7 @@
         <v>26</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="11:17">
@@ -6447,10 +6444,10 @@
         <v>29</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>26</v>
@@ -6462,7 +6459,7 @@
         <v>26</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="11:17">
@@ -6470,10 +6467,10 @@
         <v>30</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>26</v>
@@ -6485,7 +6482,7 @@
         <v>26</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="11:17">
@@ -6493,13 +6490,13 @@
         <v>31</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>26</v>
@@ -6508,7 +6505,7 @@
         <v>26</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="11:17">
@@ -6516,7 +6513,7 @@
         <v>32</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>21</v>
@@ -6531,7 +6528,7 @@
         <v>26</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="11:17">
@@ -6539,7 +6536,7 @@
         <v>33</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>21</v>
@@ -6554,7 +6551,7 @@
         <v>26</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="11:17">
@@ -6562,7 +6559,7 @@
         <v>34</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>21</v>
@@ -6577,7 +6574,7 @@
         <v>26</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="11:17">
@@ -6585,7 +6582,7 @@
         <v>35</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>21</v>
@@ -6600,7 +6597,7 @@
         <v>26</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" spans="11:17">
@@ -6608,7 +6605,7 @@
         <v>36</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>21</v>
@@ -6623,7 +6620,7 @@
         <v>26</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="11:17">
@@ -6631,7 +6628,7 @@
         <v>37</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>21</v>
@@ -6646,7 +6643,7 @@
         <v>26</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="11:17">
@@ -6654,7 +6651,7 @@
         <v>38</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>21</v>
@@ -6669,7 +6666,7 @@
         <v>26</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="11:17">
@@ -6677,13 +6674,13 @@
         <v>39</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>26</v>
@@ -6700,7 +6697,7 @@
         <v>40</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>21</v>
@@ -6715,7 +6712,7 @@
         <v>26</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="11:17">
@@ -6723,13 +6720,13 @@
         <v>41</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>26</v>
@@ -6746,7 +6743,7 @@
         <v>42</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>21</v>
@@ -6761,7 +6758,7 @@
         <v>26</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" spans="11:17">
@@ -6769,13 +6766,13 @@
         <v>43</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>26</v>
@@ -6792,7 +6789,7 @@
         <v>44</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>21</v>
@@ -6807,7 +6804,7 @@
         <v>26</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="11:17" ht="54">
@@ -6815,13 +6812,13 @@
         <v>45</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="O48" s="1" t="s">
         <v>26</v>

--- a/document/Scene.xlsx
+++ b/document/Scene.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sekiguchi\Documents\HouseholdAccountBook\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2981CE-4FF8-48BD-BD19-B4BF70DEBA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FF9F7B-F42C-46F4-BF50-A0A57F06BE65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="画面一覧" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="203">
   <si>
     <t>画面一覧</t>
     <rPh sb="0" eb="4">
@@ -3452,8 +3452,8 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>71467</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>154121</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>122371</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5561,7 +5561,7 @@
         <v>26</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="11:17">
@@ -5587,7 +5587,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="11:17" ht="36">
+    <row r="18" spans="11:17">
       <c r="K18" s="3">
         <v>15</v>
       </c>
@@ -5606,11 +5606,11 @@
       <c r="P18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q18" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="11:17" ht="36">
+      <c r="Q18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="11:17">
       <c r="K19" s="3">
         <v>16</v>
       </c>
@@ -5629,8 +5629,8 @@
       <c r="P19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q19" s="4" t="s">
-        <v>103</v>
+      <c r="Q19" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="11:17">
@@ -5676,7 +5676,7 @@
         <v>26</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="11:17">
@@ -5702,28 +5702,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="11:17" ht="36">
+    <row r="23" spans="11:17">
       <c r="K23" s="3">
         <v>20</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>88</v>
-      </c>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
       <c r="N23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q23" s="4" t="s">
-        <v>95</v>
-      </c>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="4"/>
     </row>
     <row r="24" spans="11:17">
       <c r="K24" s="3">
